--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/Documentación/Historias de Usuario y criterios de aceptación SIGET.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/Documentación/Historias de Usuario y criterios de aceptación SIGET.xlsx
@@ -775,22 +775,22 @@
     <t xml:space="preserve">Con la finalidad de asignar responsables, atender las solicitudes y mantener actualizado su estado.</t>
   </si>
   <si>
-    <t xml:space="preserve">Asignación o reasignación de ticket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En caso que exista un ticket pendiente de asignación o que requiera cambio de responsable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuando el Administrador del sistema asigna o reasigna el ticket a un Técnico de soporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema registra al Técnico responsable y mantiene trazabilidad de la asignación o reasignación</t>
+    <t xml:space="preserve">Asignación administrativa y toma de tickets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En caso que exista un ticket activo sin Técnico responsable, o que se requiera asignar o reasignar un ticket activo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuando el Administrador asigna o reasigna el ticket, o un Técnico toma para sí un ticket sin responsable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sistema registra al responsable y audita la operación. Solo el Administrador puede asignar a otro Técnico o reasignar. Ante tomas simultáneas solo una confirma, sin sobrescribir al responsable.</t>
   </si>
   <si>
     <t xml:space="preserve">Atención y cambio de estado</t>
   </si>
   <si>
-    <t xml:space="preserve">En caso que el técnico tenga un ticket asignado</t>
+    <t xml:space="preserve">En caso que el Técnico sea el responsable asignado del ticket</t>
   </si>
   <si>
     <t xml:space="preserve">Cuando el Técnico registra la atención realizada o modifica el estado del ticket</t>
@@ -811,16 +811,16 @@
     <t xml:space="preserve">El sistema informa que el ticket no existe</t>
   </si>
   <si>
-    <t xml:space="preserve">Ticket cerrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En caso que el ticket se encuentre cerrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuando el técnico intenta modificarlo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema informa que el ticket se encuentra cerrado y no permite modificarlo</t>
+    <t xml:space="preserve">Ticket cerrado o toma no permitida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En caso que el ticket esté cerrado, o que al intentar tomarlo esté resuelto o asignado a otro Técnico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuando el Técnico intenta modificar el ticket cerrado o tomar un ticket no disponible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sistema rechaza la operación sin modificar el ticket, su estado ni su responsable.</t>
   </si>
   <si>
     <t>E5-H15</t>
@@ -1816,38 +1816,38 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -1856,42 +1856,42 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="none"/>
@@ -5164,7 +5164,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" ht="15">
+    <row r="72" ht="80.25" customHeight="1">
       <c r="A72" s="1"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -5202,7 +5202,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" ht="15">
+    <row r="73" ht="63.75" customHeight="1">
       <c r="A73" s="1"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -5240,7 +5240,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" ht="15">
+    <row r="74" ht="84" customHeight="1">
       <c r="A74" s="1"/>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>

--- a/Fase 2/Evidencias Proyecto/Evidencias de documentación/Documentación/Historias de Usuario y criterios de aceptación SIGET.xlsx
+++ b/Fase 2/Evidencias Proyecto/Evidencias de documentación/Documentación/Historias de Usuario y criterios de aceptación SIGET.xlsx
@@ -967,10 +967,10 @@
     <t xml:space="preserve">En caso que La falla del activo es irreparable o su costo excede el valor del equipo.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuando El técnico selecciona la opción "Dar de Baja / No Reparable".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El sistema cambia el estado del equipo a "De Baja", registra el informe técnico de descarte y notifica al administrador de inventario.</t>
+    <t xml:space="preserve">Cuando el Técnico selecciona "Dar de Baja / No Reparable" e ingresa el informe técnico de descarte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sistema registra el informe técnico de descarte y el resultado "No reparable", completa la OT en estado "Completada", cambia el activo a "Dado de baja" y el ticket a "Resuelto", y notifica al administrador de inventario. El ticket pasa posteriormente a "Cerrado" mediante el flujo habitual de gestión de tickets. La OT queda finalizada aunque el equipo no recupere su operatividad.</t>
   </si>
   <si>
     <t xml:space="preserve">Orden ya cerrada previamente</t>
@@ -2506,7 +2506,7 @@
     <col customWidth="1" min="7" max="7" width="26.57"/>
     <col customWidth="1" min="8" max="8" width="27.43"/>
     <col customWidth="1" min="9" max="9" width="21.289999999999999"/>
-    <col customWidth="1" min="10" max="10" width="22.43"/>
+    <col customWidth="1" min="10" max="10" width="34.57421875"/>
     <col customWidth="1" min="11" max="26" width="11.43"/>
   </cols>
   <sheetData>
@@ -4930,7 +4930,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" ht="15">
+    <row r="66" ht="42.75">
       <c r="A66" s="1"/>
       <c r="B66" s="22" t="s">
         <v>233</v>
@@ -4976,7 +4976,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" ht="15">
+    <row r="67" ht="42.75">
       <c r="A67" s="1"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -5014,7 +5014,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" ht="15">
+    <row r="68" ht="42.75">
       <c r="A68" s="1"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -5052,7 +5052,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" ht="15">
+    <row r="69" ht="71.25">
       <c r="A69" s="1"/>
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
@@ -5118,7 +5118,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" ht="15">
+    <row r="71" ht="85.5">
       <c r="A71" s="1"/>
       <c r="B71" s="22" t="s">
         <v>248</v>
@@ -5306,7 +5306,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" ht="15">
+    <row r="76" ht="28.5">
       <c r="A76" s="1"/>
       <c r="B76" s="22" t="s">
         <v>268</v>
@@ -5352,7 +5352,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" ht="15">
+    <row r="77" ht="42.75">
       <c r="A77" s="1"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -5390,7 +5390,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" ht="15">
+    <row r="78" ht="42.75">
       <c r="A78" s="1"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -5428,7 +5428,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" ht="15">
+    <row r="79" ht="28.5">
       <c r="A79" s="1"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -5494,7 +5494,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" ht="15">
+    <row r="81" ht="128.25">
       <c r="A81" s="1"/>
       <c r="B81" s="22" t="s">
         <v>284</v>
@@ -5540,7 +5540,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" ht="15">
+    <row r="82" ht="57">
       <c r="A82" s="1"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -5578,7 +5578,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" ht="15">
+    <row r="83" ht="57">
       <c r="A83" s="1"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -5616,7 +5616,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" ht="15">
+    <row r="84" ht="42.75">
       <c r="A84" s="1"/>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
@@ -5682,7 +5682,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" ht="15">
+    <row r="86" ht="85.5">
       <c r="A86" s="1"/>
       <c r="B86" s="22" t="s">
         <v>303</v>
@@ -5728,7 +5728,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" ht="15">
+    <row r="87" ht="42.75">
       <c r="A87" s="1"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -5766,7 +5766,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" ht="15">
+    <row r="88" ht="198" customHeight="1">
       <c r="A88" s="1"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -5804,7 +5804,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" ht="15">
+    <row r="89" ht="42.75">
       <c r="A89" s="1"/>
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
@@ -5870,7 +5870,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" ht="15">
+    <row r="91" ht="57">
       <c r="A91" s="1"/>
       <c r="B91" s="22" t="s">
         <v>322</v>
@@ -5916,7 +5916,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" ht="15">
+    <row r="92" ht="42.75">
       <c r="A92" s="1"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -5954,7 +5954,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" ht="15">
+    <row r="93" ht="42.75">
       <c r="A93" s="1"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -5992,7 +5992,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" ht="15">
+    <row r="94" ht="42.75">
       <c r="A94" s="1"/>
       <c r="B94" s="15"/>
       <c r="C94" s="15"/>
@@ -6058,7 +6058,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" ht="15">
+    <row r="96" ht="71.25">
       <c r="A96" s="1"/>
       <c r="B96" s="22" t="s">
         <v>341</v>
@@ -6104,7 +6104,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" ht="15">
+    <row r="97" ht="42.75">
       <c r="A97" s="1"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -6142,7 +6142,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" ht="15">
+    <row r="98" ht="71.25">
       <c r="A98" s="1"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -6180,7 +6180,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" ht="15">
+    <row r="99" ht="57">
       <c r="A99" s="1"/>
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
@@ -6246,7 +6246,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" ht="15">
+    <row r="101" ht="71.25">
       <c r="A101" s="1"/>
       <c r="B101" s="22" t="s">
         <v>360</v>
@@ -6292,7 +6292,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" ht="15">
+    <row r="102" ht="71.25">
       <c r="A102" s="1"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -6330,7 +6330,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" ht="15">
+    <row r="103" ht="42.75">
       <c r="A103" s="1"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -6368,7 +6368,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" ht="15">
+    <row r="104" ht="57">
       <c r="A104" s="1"/>
       <c r="B104" s="15"/>
       <c r="C104" s="15"/>
@@ -6434,7 +6434,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" ht="15">
+    <row r="106" ht="71.25">
       <c r="A106" s="1"/>
       <c r="B106" s="22" t="s">
         <v>379</v>
@@ -6480,7 +6480,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" ht="15">
+    <row r="107" ht="42.75">
       <c r="A107" s="1"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -6518,7 +6518,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" ht="15">
+    <row r="108" ht="57">
       <c r="A108" s="1"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -6556,7 +6556,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" ht="15">
+    <row r="109" ht="42.75">
       <c r="A109" s="1"/>
       <c r="B109" s="15"/>
       <c r="C109" s="15"/>
@@ -6622,7 +6622,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" ht="15">
+    <row r="111" ht="57">
       <c r="A111" s="1"/>
       <c r="B111" s="22" t="s">
         <v>398</v>
@@ -6668,7 +6668,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" ht="15">
+    <row r="112" ht="57">
       <c r="A112" s="1"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -6706,7 +6706,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" ht="15">
+    <row r="113" ht="57">
       <c r="A113" s="1"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -6744,7 +6744,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114" ht="15">
+    <row r="114" ht="42.75">
       <c r="A114" s="1"/>
       <c r="B114" s="15"/>
       <c r="C114" s="15"/>
@@ -6810,7 +6810,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116" ht="15">
+    <row r="116" ht="57">
       <c r="A116" s="1"/>
       <c r="B116" s="22" t="s">
         <v>417</v>
@@ -6856,7 +6856,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117" ht="15">
+    <row r="117" ht="57">
       <c r="A117" s="1"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -6894,7 +6894,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118" ht="15">
+    <row r="118" ht="71.25">
       <c r="A118" s="1"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -6932,7 +6932,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119" ht="15">
+    <row r="119" ht="85.5">
       <c r="A119" s="1"/>
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
@@ -6998,7 +6998,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" ht="15">
+    <row r="121" ht="71.25">
       <c r="A121" s="1"/>
       <c r="B121" s="22" t="s">
         <v>436</v>
@@ -7044,7 +7044,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" ht="15">
+    <row r="122" ht="85.5">
       <c r="A122" s="1"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -7082,7 +7082,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" ht="15">
+    <row r="123" ht="57">
       <c r="A123" s="1"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -7120,7 +7120,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" ht="15">
+    <row r="124" ht="42.75">
       <c r="A124" s="1"/>
       <c r="B124" s="15"/>
       <c r="C124" s="15"/>
@@ -7186,7 +7186,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" ht="15">
+    <row r="126" ht="71.25">
       <c r="A126" s="1"/>
       <c r="B126" s="31" t="s">
         <v>455</v>
@@ -7232,7 +7232,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" ht="15">
+    <row r="127" ht="57">
       <c r="A127" s="1"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -7270,7 +7270,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128" ht="15">
+    <row r="128" ht="71.25">
       <c r="A128" s="1"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
